--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\AppData\Local\Packages\5319275A.WhatsAppDesktop_cv1g1gvanyjgm\LocalState\sessions\45B24722FE38F8552C914ACD95972103A868DC89\transfers\2026-32\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ABAA53-0AFE-4AF0-92A2-2BA1B9F8AF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AA6C58-0F69-48A6-A741-17CF1DA34E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,15 @@
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -197,6 +206,9 @@
   </si>
   <si>
     <t>Normal</t>
+  </si>
+  <si>
+    <t>normal</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1004,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="9">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="G6" s="9">
         <v>6</v>
@@ -1002,11 +1014,11 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>650</v>
+        <v>770</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>790</v>
+        <v>670</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -1022,68 +1034,128 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B7" s="14">
+        <v>420</v>
+      </c>
+      <c r="C7" s="14">
+        <v>0</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>20</v>
+      </c>
+      <c r="F7" s="14">
+        <v>200</v>
+      </c>
+      <c r="G7" s="14">
+        <v>4</v>
+      </c>
+      <c r="H7" s="14">
+        <v>30</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
+        <v>710</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="M7" s="16"/>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>350</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="14">
+        <v>300</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="M8" s="16"/>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>0</v>
+      </c>
+      <c r="D9" s="14">
+        <v>60</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14">
+        <v>90</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="M9" s="16"/>
       <c r="N9" s="17"/>
     </row>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AA6C58-0F69-48A6-A741-17CF1DA34E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275389F7-F721-4489-8910-617DE21BE1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,15 @@
   </si>
   <si>
     <t>normal</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1081,9 @@
       <c r="L7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="16"/>
+      <c r="M7" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1160,156 +1171,293 @@
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46248</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>90</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>450</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
+        <v>990</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M10" s="16"/>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B11">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
+        <v>780</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="M11" s="16"/>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B12" s="14">
+        <v>510</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>90</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
+        <v>750</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M12" s="16"/>
       <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>75</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
+        <v>475</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B14" s="14">
+        <v>390</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>150</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>0</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="M14" s="16"/>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B15" s="14">
+        <v>450</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>150</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="M15" s="16"/>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>100</v>
+      </c>
+      <c r="G16" s="14">
+        <v>2</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M16" s="16"/>
       <c r="N16" s="17"/>
     </row>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275389F7-F721-4489-8910-617DE21BE1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE6018C-8336-45B4-AFD0-75D4B4352EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t>Satisfied</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1456,162 +1465,288 @@
         <v>59</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M16" s="16"/>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
+      <c r="A17" s="13">
+        <v>46255</v>
+      </c>
       <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
+        <v>950</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="13">
+        <v>46256</v>
+      </c>
       <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
+        <v>1200</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="M18" s="16"/>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+      <c r="A19" s="13">
+        <v>46257</v>
+      </c>
       <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>120</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
+        <v>1200</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="M19" s="16"/>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13">
+        <v>46258</v>
+      </c>
       <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>90</v>
+      </c>
+      <c r="E20" s="14">
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
+        <v>960</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="M20" s="16"/>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
+      <c r="A21" s="13">
+        <v>46259</v>
+      </c>
       <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
+        <v>910</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="M21" s="16"/>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="13">
+        <v>46260</v>
+      </c>
       <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>90</v>
+      </c>
+      <c r="E22" s="14">
+        <v>90</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
+        <v>960</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M22" s="16"/>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
+      <c r="A23" s="13">
+        <v>46261</v>
+      </c>
       <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="C23" s="14">
+        <v>0</v>
+      </c>
+      <c r="D23" s="14">
+        <v>90</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
+        <v>1060</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="M23" s="16"/>
       <c r="N23" s="17"/>
     </row>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE6018C-8336-45B4-AFD0-75D4B4352EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73762AC-80B4-47E1-BB93-04DAA15A26FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t>satishfied</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1480,9 @@
       <c r="A17" s="13">
         <v>46255</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
       <c r="C17" s="14">
         <v>0</v>
       </c>
@@ -1495,11 +1503,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>490</v>
+        <v>970</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>470</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1514,7 +1522,9 @@
       <c r="A18" s="13">
         <v>46256</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
       <c r="C18" s="14">
         <v>0</v>
       </c>
@@ -1535,11 +1545,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>720</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>59</v>
@@ -1554,7 +1564,9 @@
       <c r="A19" s="13">
         <v>46257</v>
       </c>
-      <c r="B19" s="14"/>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
       <c r="C19" s="14">
         <v>0</v>
       </c>
@@ -1575,11 +1587,11 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>240</v>
+        <v>720</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>58</v>
@@ -1594,7 +1606,9 @@
       <c r="A20" s="13">
         <v>46258</v>
       </c>
-      <c r="B20" s="14"/>
+      <c r="B20" s="14">
+        <v>410</v>
+      </c>
       <c r="C20" s="14">
         <v>0</v>
       </c>
@@ -1615,11 +1629,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>890</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>550</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>58</v>
@@ -1634,7 +1648,9 @@
       <c r="A21" s="13">
         <v>46259</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
       <c r="C21" s="14">
         <v>0</v>
       </c>
@@ -1655,11 +1671,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>530</v>
+        <v>950</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>910</v>
+        <v>490</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>58</v>
@@ -1674,7 +1690,9 @@
       <c r="A22" s="13">
         <v>46260</v>
       </c>
-      <c r="B22" s="14"/>
+      <c r="B22" s="14">
+        <v>450</v>
+      </c>
       <c r="C22" s="14">
         <v>0</v>
       </c>
@@ -1695,11 +1713,11 @@
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>480</v>
+        <v>930</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>510</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>58</v>
@@ -1714,7 +1732,9 @@
       <c r="A23" s="13">
         <v>46261</v>
       </c>
-      <c r="B23" s="14"/>
+      <c r="B23" s="14">
+        <v>440</v>
+      </c>
       <c r="C23" s="14">
         <v>0</v>
       </c>
@@ -1735,11 +1755,11 @@
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>380</v>
+        <v>820</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>1060</v>
+        <v>620</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>58</v>
@@ -1751,266 +1771,506 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>60</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>0</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
+        <v>670</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="M24" s="16"/>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M25" s="16"/>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="14">
+        <v>450</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>70</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
+        <v>860</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M26" s="16"/>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B27" s="14">
+        <v>450</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>70</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M27" s="16"/>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B28" s="14">
+        <v>450</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14">
+        <v>90</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B29" s="14">
+        <v>450</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>80</v>
+      </c>
+      <c r="E29" s="14">
+        <v>80</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
+        <v>530</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M29" s="16"/>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B30" s="14">
+        <v>450</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>90</v>
+      </c>
+      <c r="F30" s="14">
+        <v>100</v>
+      </c>
+      <c r="G30" s="14">
+        <v>2</v>
+      </c>
+      <c r="H30" s="14">
+        <v>0</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
+        <v>650</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B31" s="14">
+        <v>460</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>90</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B32" s="14">
+        <v>470</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>90</v>
+      </c>
+      <c r="E32" s="14">
+        <v>85</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>705</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
+        <v>735</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>64</v>
+      </c>
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B33" s="14">
+        <v>430</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>90</v>
+      </c>
+      <c r="E33" s="14">
+        <v>80</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>0</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
+        <v>780</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M33" s="16"/>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B34" s="14">
+        <v>460</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>90</v>
+      </c>
+      <c r="E34" s="14">
+        <v>45</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>0</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+        <v>535</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B35" s="14">
+        <v>460</v>
+      </c>
+      <c r="C35" s="14">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14">
+        <v>45</v>
+      </c>
+      <c r="F35" s="14">
+        <v>250</v>
+      </c>
+      <c r="G35" s="14">
+        <v>5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>0</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
+        <v>535</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
     </row>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73762AC-80B4-47E1-BB93-04DAA15A26FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D608A5E8-6A67-4373-9B1A-A4E12B5B189C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2275,24 +2275,44 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>60</v>
+      </c>
+      <c r="D36" s="14">
+        <v>30</v>
+      </c>
+      <c r="E36" s="14">
+        <v>30</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>0</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M36" s="16"/>
       <c r="N36" s="17"/>
     </row>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D608A5E8-6A67-4373-9B1A-A4E12B5B189C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1293944-3D64-4B6C-B68E-B7D0BABF8E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2317,24 +2317,44 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B37" s="14">
+        <v>100</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <v>15</v>
+      </c>
+      <c r="F37" s="14">
+        <v>2</v>
+      </c>
+      <c r="G37" s="14">
+        <v>2</v>
+      </c>
+      <c r="H37" s="14">
+        <v>60</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>237</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
+        <v>1203</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M37" s="16"/>
       <c r="N37" s="17"/>
     </row>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1293944-3D64-4B6C-B68E-B7D0BABF8E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB17A4A9-8EE0-46E1-84C1-A68689E46C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>satishfied</t>
+  </si>
+  <si>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -2321,7 +2324,7 @@
         <v>46275</v>
       </c>
       <c r="B37" s="14">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="C37" s="14">
         <v>60</v>
@@ -2343,11 +2346,11 @@
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>237</v>
+        <v>457</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>1203</v>
+        <v>983</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>49</v>
@@ -2359,46 +2362,86 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>60</v>
+      </c>
+      <c r="E38" s="14">
+        <v>45</v>
+      </c>
+      <c r="F38" s="14">
+        <v>300</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>60</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+        <v>555</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M38" s="16"/>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B39" s="14">
+        <v>500</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>60</v>
+      </c>
+      <c r="E39" s="14">
+        <v>45</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>120</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>725</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+        <v>715</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M39" s="16"/>
       <c r="N39" s="17"/>
     </row>
